--- a/05-halcyon-ai-governance/artifacts/ai_system_inventory.xlsx
+++ b/05-halcyon-ai-governance/artifacts/ai_system_inventory.xlsx
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>EU AI Act high-risk obligations were originally applicable 2 August 2026. A May 2026 'Digital Omnibus' proposal would defer standalone high-risk systems to 2 December 2027. As of this inventory that deferral is proposed, not adopted. Plans here assume the earlier date until the text is final — planning to the later date and being wrong is the costlier error.</t>
+          <t>EU AI Act high-risk obligations were originally applicable 2 August 2026. The Digital Omnibus on AI (Regulation (EU) 2026/1744) entered into force 27 July 2026 and deferred standalone Annex III high-risk obligations to 2 December 2027 (embedded Annex I systems to 2 August 2028). The deferral is selective: Article 50 transparency duties, the Article 5 prohibitions, and GPAI provider obligations were not deferred and applied from 2 August 2026. Plans here use the enacted 2 December 2027 date for standalone high-risk systems and the unchanged 2 August 2026 date for transparency duties.</t>
         </is>
       </c>
     </row>
